--- a/data/btc_price_fred.xlsx
+++ b/data/btc_price_fred.xlsx
@@ -55197,7 +55197,7 @@
         <v>46220</v>
       </c>
       <c r="B4213" t="n">
-        <v>63931.55078125</v>
+        <v>63965.390625</v>
       </c>
       <c r="C4213" t="inlineStr">
         <is>
